--- a/光伏配储项目/电价数据/2026/腰古湾站.xlsx
+++ b/光伏配储项目/电价数据/2026/腰古湾站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50992</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.5331</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.54383</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43864</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45545</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44023</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40257</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41508</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42506</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41353</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25241</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>-0.01258</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.11461</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.03088</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.02296</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03636</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08247</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14434</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21155</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23898</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15084</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01386</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11871</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.01235</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.09361</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.07940999999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.18532</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42804</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.17977</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.44383</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.07309</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.24151</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.5602</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.60278</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.22424</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47873</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42084</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.15361</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.69257</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79434</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53661</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50637</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.4649</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50013</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47386</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5138400000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6238899999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72519</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43612</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.13042</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.16583</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12361</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.25724</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.1945</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.14807</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.12619</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.16291</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.0005899999999999999</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.05961</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.11565</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.27508</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.14318</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.25531</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.21019</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.27571</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>-0.00222</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>-0.04245</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.03179</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>-0.01313</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22634</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.2768</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67852</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.78088</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.76639</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.78716</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.47518</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.13478</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.44017</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6003999999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44026</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33312</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5164500000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48546</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.21095</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.0137</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.26224</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.24859</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28051</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.27404</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.25805</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.13769</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.09195</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.23041</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27453</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.01594</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.16909</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27784</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.2018</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.15634</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.00429</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.08534</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.05598</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.1939</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.26522</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>-0.004860000000000001</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.07781</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.20633</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.22717</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.21325</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.05572999999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.14187</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.09122</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.10118</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.24126</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.22399</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.27656</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34321</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.09723000000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.24925</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.24916</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46913</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29733</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2942</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.24807</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28207</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.05395</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.00536</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.03511</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.00966</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26959</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.07253</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.16689</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.12406</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.00376</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.03847</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.02267</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.27714</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.02889</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.09061</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>-0.02221</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.02076</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.15965</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.02997</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.16907</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>-0.008070000000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29584</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28664</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25886</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03635</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04409</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.03926</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.03921</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.01939</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04469</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04848</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.04991</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14816</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.05098</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.14687</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.18581</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.27204</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.17642</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.2101</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.11561</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.21762</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.30227</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41339</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34889</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.24802</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.01371</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.28593</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28173</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.04846</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04466</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10101</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00269</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04586</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04874</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04840999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04882</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04243</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04831000000000001</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04349</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.07074</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.17708</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.25465</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2469</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.14397</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.21604</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.19251</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.22176</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.19545</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.21674</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.19622</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.24282</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.23603</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.25832</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33051</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31864</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2584</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.10205</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.24673</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.25967</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.24565</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.08061</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.05903</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17177</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14839</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16012</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15935</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23739</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21477</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.17532</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.11945</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28641</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.25829</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.25553</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.25491</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>-0.04208</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.28067</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.25629</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.01471</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.11903</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.07226</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.14958</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.10773</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>-0.00251</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.0526</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.10761</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.17734</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.27417</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.16634</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.07726999999999999</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.20458</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47798</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7396</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.4896</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.23489</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.57524</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.51998</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.20726</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.48844</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0.93425</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>-0.01329</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.48896</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0.6890499999999999</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.47404</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>0.9807400000000001</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0.69962</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7900199999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303300000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7873300000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77676</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87854</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8733500000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49223</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39911</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20623</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87936</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5513400000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63895</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49862</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45902</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42748</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44132</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45124</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42116</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43394</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.39583</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40088</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58705</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42764</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59622</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.45399</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.65501</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.82267</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>-0.04143</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>-0.04744</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.83039</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>-0.04639</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>-0.04604999999999999</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.04709000000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>-0.04603</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.09912</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.07478</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.10062</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.07174</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.09301000000000001</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.06412000000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.08219</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.0439</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.06346</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.13933</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.07204000000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.05048</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.06506999999999999</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>-0.02536</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.06758</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.07708</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.12833</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.13428</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.11781</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.22381</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45348</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35435</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9549500000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47724</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.06176</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.22805</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.04726</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.25986</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.09672</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.27101</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.25142</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.10164</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2542</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27197</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.19324</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28258</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5967</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88522</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33308</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13543</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70345</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7951699999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6496799999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58348</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43745</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50052</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.01089</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.23287</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.17345</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>-0.04721</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.22096</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.23069</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.19076</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.03856</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>-0.008119999999999999</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>-0.02953</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>-0.04287</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.13122</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.05557</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.28477</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.03153</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.19603</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32475</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42456</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27295</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.03548</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.25078</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14913</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14781</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15246</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.5724</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.60551</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14431</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14421</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14166</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14863</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14953</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28042</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14678</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.13162</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11772</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11825</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.17492</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14545</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15357</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4407799999999999</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54244</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46864</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30618</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.04145</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.03477</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.23578</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24399</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26259</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.25445</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22797</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28782</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.24887</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.26465</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.18244</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36024</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3898</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34268</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.26036</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.2532</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.23733</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24908</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.18352</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.06912</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.16702</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24095</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27867</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.25315</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.23597</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.27866</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.25513</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.47057</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70711</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41036</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.26312</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2975</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.27466</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34922</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5764</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42966</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6513300000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8336</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47293</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34484</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25998</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13164</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.2434</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.04844</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.12641</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.22545</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.23669</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14238</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.19443</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.20472</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.27914</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.28298</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.27905</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63576</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60237</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59201</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45489</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.62109</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.45333</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.42865</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4773</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36017</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48989</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.41932</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.42492</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56088</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50078</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.40975</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.19248</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43827</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.18934</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.01334</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.01547</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.20482</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.08740000000000001</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.04245</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.26296</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.71025</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.23183</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.09048</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.03865</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.20733</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48019</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4227</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50504</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50632</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.5171699999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.60462</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.52316</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.45779</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5319400000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8065099999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.74202</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5931799999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64167</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.47997</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47949</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47284</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.49873</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44524</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45841</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43693</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45771</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40711</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.2234</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.23955</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15392</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.19476</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.41558</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.06331000000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.23689</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41917</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.47474</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46564</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.50081</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47635</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.01381</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.19003</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39671</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40583</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36407</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44226</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.13128</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.2314</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23293</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.22692</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24604</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.02443</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.12937</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.22436</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.02378</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.14896</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25506</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.03646</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1512</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.00488</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21556</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22629</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.13873</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21038</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2648</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28286</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25781</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35196</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22765</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21713</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15123</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.18066</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00321</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04384</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04129</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03406</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04317</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.17014</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21501</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2675</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24249</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24497</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24474</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25037</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26389</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26904</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25815</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26596</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26815</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27419</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25682</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25244</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23693</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.19101</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05738</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06675</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.25049</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.2274</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22476</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26973</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26352</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24603</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22325</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20684</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.19026</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2151</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.2259</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.17044</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.19034</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22284</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.22259</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24402</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23227</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21547</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22707</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.27004</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24789</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18441</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06644</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.49749</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.50161</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.50492</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.02409</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.18311</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.19648</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09841</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.04394</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.04867</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.00605</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.2076</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.03171</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04722999999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02715</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03962</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.07452</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02656</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.02225</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02235</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.05247</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.20636</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.22899</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.25712</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.26189</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.25892</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.28768</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.26293</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.27923</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.25675</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.28805</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.26452</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.27965</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32496</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.08731999999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-0.00751</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.0171</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>-0.008880000000000001</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>-0.02374</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.23643</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.26422</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.28202</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.25791</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.09994</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.21385</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26942</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.13818</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.04782</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.01683</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33078</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.26335</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.00747</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5227000000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.26022</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.26457</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.24148</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.2099</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.23625</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.22391</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.20448</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.20599</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27035</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.20554</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.23832</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.24256</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.17287</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2286</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.27217</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.25626</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.22559</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.24772</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41829</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.43061</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.43077</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.27536</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.42481</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.70526</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.41919</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40271</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45864</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36876</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40098</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.09146</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.27856</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.02713</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>-0.02575</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.02217</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.03775999999999999</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>-0.01777</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.27966</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.09054999999999999</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.16752</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.29045</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.25903</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.14734</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.15196</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.18448</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.01958</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.07226</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.26228</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.26564</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.4288</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.52788</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.52297</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45801</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54826</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.42686</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.44257</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.4965</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.47784</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7085900000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.74749</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5163300000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.51822</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37525</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27138</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.25931</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.25876</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20581</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23164</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.13489</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01394</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02467</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24123</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.01925</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02448</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.00899</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>-0.0009300000000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.12038</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11159</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.20552</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18457</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.10729</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.23527</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.22824</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.2203</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.26572</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37617</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.76273</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38222</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.26638</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.23664</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.21484</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.20593</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.17407</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.17397</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.17914</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.23294</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.06328</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.01897</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.03025</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.01375</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.08114</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.01117</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.02818</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01337</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.03197</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.03944</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.02249</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.03993</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>-0.03832</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.02744</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13412</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.01367</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.14187</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.16193</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.20525</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>-0.0112</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.01499</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.08016</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.46381</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.48048</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.43884</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.53527</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.47049</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.41615</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44368</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.39072</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.49863</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25873</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.22331</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.20372</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.18227</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22275</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.20979</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13194</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.14088</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.01709</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.11424</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03212</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.03404</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.03538</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.03852000000000001</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.03119</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03737</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.0247</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.0334</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.08846999999999999</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.04178</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.04683</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.04195</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.03283</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.04105</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.0327</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.02367</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-0.0369</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.02651</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.1832</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21608</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23618</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23973</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.24583</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.26112</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.26741</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26909</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.28784</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47888</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43487</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39514</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38401</v>
       </c>
     </row>
   </sheetData>
